--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>username</t>
   </si>
@@ -31,7 +31,19 @@
     <t>engineer@bescom.co.in</t>
   </si>
   <si>
+    <t>rajesh@bescom.co.in</t>
+  </si>
+  <si>
+    <t>test@bescom.in</t>
+  </si>
+  <si>
+    <t>admin@bescom.in</t>
+  </si>
+  <si>
     <t>ENGINEER</t>
+  </si>
+  <si>
+    <t>admin</t>
   </si>
 </sst>
 </file>
@@ -393,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -415,13 +427,55 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2">
         <v>46141.7563509375</v>
       </c>
       <c r="D2" s="2">
-        <v>46141.76149749096</v>
+        <v>46148.7835945949</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46148.71559585648</v>
+      </c>
+      <c r="D3" s="2">
+        <v>46148.71559585648</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2">
+        <v>46149.64288136574</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46149.8111499537</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46149.711615625</v>
+      </c>
+      <c r="D5" s="2">
+        <v>46149.83499411847</v>
       </c>
     </row>
   </sheetData>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -447,7 +447,7 @@
         <v>46148.71559585648</v>
       </c>
       <c r="D3" s="2">
-        <v>46148.71559585648</v>
+        <v>46149.868529274</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -475,7 +475,7 @@
         <v>46149.711615625</v>
       </c>
       <c r="D5" s="2">
-        <v>46149.83499411847</v>
+        <v>46149.86622034722</v>
       </c>
     </row>
   </sheetData>
